--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss358115\Desktop\Keeperメニュー\Keeperメニュー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{4EC85CAB-E493-8D44-965B-6C08A91B479E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{6BD8A32C-5766-B441-9EEE-8CBAD758E13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="26">
   <si>
     <t>商品名</t>
   </si>
@@ -120,6 +120,9 @@
       <t>センシャ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KeePer施工車限定</t>
   </si>
 </sst>
 </file>
@@ -475,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
     <col min="4" max="4" width="9.1328125" style="3" bestFit="1" customWidth="1"/>
@@ -1989,6 +1992,90 @@
         <v>67760</v>
       </c>
     </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A92" t="s">
+        <v>24</v>
+      </c>
+      <c r="B92" t="s">
+        <v>14</v>
+      </c>
+      <c r="C92" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A93" t="s">
+        <v>24</v>
+      </c>
+      <c r="B93" t="s">
+        <v>14</v>
+      </c>
+      <c r="C93" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A94" t="s">
+        <v>24</v>
+      </c>
+      <c r="B94" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A95" t="s">
+        <v>24</v>
+      </c>
+      <c r="B95" t="s">
+        <v>14</v>
+      </c>
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A96" t="s">
+        <v>24</v>
+      </c>
+      <c r="B96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A97" t="s">
+        <v>24</v>
+      </c>
+      <c r="B97" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="3">
+        <v>540</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss358115\Desktop\Keeperメニュー\Keeperメニュー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{6BD8A32C-5766-B441-9EEE-8CBAD758E13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{472B4AAD-49E7-FF4A-8FA1-D4DE9DA54E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="26">
   <si>
     <t>商品名</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>KeePer施工車限定</t>
+  </si>
+  <si>
+    <t>Keeper部分施工</t>
   </si>
 </sst>
 </file>
@@ -478,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
     <col min="4" max="4" width="9.1328125" style="3" bestFit="1" customWidth="1"/>
@@ -2050,7 +2053,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A96" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B96" t="s">
         <v>14</v>
@@ -2062,9 +2065,9 @@
         <v>540</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.1">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A97" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B97" t="s">
         <v>14</v>
@@ -2074,6 +2077,654 @@
       </c>
       <c r="D97" s="3">
         <v>540</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A98" t="s">
+        <v>25</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" s="3">
+        <f t="shared" ref="D98:D133" si="2">SUM(E98)*1</f>
+        <v>124960</v>
+      </c>
+      <c r="E98" s="1">
+        <v>124960</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" s="3">
+        <f t="shared" si="2"/>
+        <v>136290</v>
+      </c>
+      <c r="E99" s="2">
+        <v>136290</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="3">
+        <f t="shared" si="2"/>
+        <v>148500</v>
+      </c>
+      <c r="E100" s="2">
+        <v>148500</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A101" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="3">
+        <f t="shared" si="2"/>
+        <v>165440</v>
+      </c>
+      <c r="E101" s="2">
+        <v>165440</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="3">
+        <f t="shared" si="2"/>
+        <v>176440</v>
+      </c>
+      <c r="E102" s="2">
+        <v>176440</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A103" t="s">
+        <v>25</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="3">
+        <f t="shared" si="2"/>
+        <v>192280</v>
+      </c>
+      <c r="E103" s="2">
+        <v>192280</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" t="s">
+        <v>17</v>
+      </c>
+      <c r="C104" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" s="3">
+        <f t="shared" si="2"/>
+        <v>68310</v>
+      </c>
+      <c r="E104" s="1">
+        <v>68310</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="3">
+        <f t="shared" si="2"/>
+        <v>74250</v>
+      </c>
+      <c r="E105" s="2">
+        <v>74250</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="3">
+        <f t="shared" si="2"/>
+        <v>80300</v>
+      </c>
+      <c r="E106" s="2">
+        <v>80300</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A107" t="s">
+        <v>25</v>
+      </c>
+      <c r="B107" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="3">
+        <f t="shared" si="2"/>
+        <v>84920</v>
+      </c>
+      <c r="E107" s="2">
+        <v>84920</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A108" t="s">
+        <v>25</v>
+      </c>
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="3">
+        <f t="shared" si="2"/>
+        <v>92180</v>
+      </c>
+      <c r="E108" s="2">
+        <v>92180</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A109" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" s="3">
+        <f t="shared" si="2"/>
+        <v>114730</v>
+      </c>
+      <c r="E109" s="2">
+        <v>114730</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A110" t="s">
+        <v>25</v>
+      </c>
+      <c r="B110" t="s">
+        <v>18</v>
+      </c>
+      <c r="C110" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" s="3">
+        <f t="shared" si="2"/>
+        <v>31020</v>
+      </c>
+      <c r="E110" s="1">
+        <v>31020</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A111" t="s">
+        <v>25</v>
+      </c>
+      <c r="B111" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" s="3">
+        <f t="shared" si="2"/>
+        <v>33330</v>
+      </c>
+      <c r="E111" s="1">
+        <v>33330</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A112" t="s">
+        <v>25</v>
+      </c>
+      <c r="B112" t="s">
+        <v>18</v>
+      </c>
+      <c r="C112" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="3">
+        <f t="shared" si="2"/>
+        <v>35970</v>
+      </c>
+      <c r="E112" s="1">
+        <v>35970</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B113" t="s">
+        <v>18</v>
+      </c>
+      <c r="C113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" s="3">
+        <f t="shared" si="2"/>
+        <v>38390</v>
+      </c>
+      <c r="E113" s="1">
+        <v>38390</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A114" t="s">
+        <v>25</v>
+      </c>
+      <c r="B114" t="s">
+        <v>18</v>
+      </c>
+      <c r="C114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="3">
+        <f t="shared" si="2"/>
+        <v>43560</v>
+      </c>
+      <c r="E114" s="1">
+        <v>43560</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A115" t="s">
+        <v>25</v>
+      </c>
+      <c r="B115" t="s">
+        <v>18</v>
+      </c>
+      <c r="C115" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="3">
+        <f t="shared" si="2"/>
+        <v>48620</v>
+      </c>
+      <c r="E115" s="1">
+        <v>48620</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A116" t="s">
+        <v>25</v>
+      </c>
+      <c r="B116" t="s">
+        <v>19</v>
+      </c>
+      <c r="C116" t="s">
+        <v>6</v>
+      </c>
+      <c r="D116" s="3">
+        <f t="shared" si="2"/>
+        <v>19690</v>
+      </c>
+      <c r="E116" s="1">
+        <v>19690</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A117" t="s">
+        <v>25</v>
+      </c>
+      <c r="B117" t="s">
+        <v>19</v>
+      </c>
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" s="3">
+        <f t="shared" si="2"/>
+        <v>22000</v>
+      </c>
+      <c r="E117" s="1">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A118" t="s">
+        <v>25</v>
+      </c>
+      <c r="B118" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="3">
+        <f t="shared" si="2"/>
+        <v>24640</v>
+      </c>
+      <c r="E118" s="1">
+        <v>24640</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A119" t="s">
+        <v>25</v>
+      </c>
+      <c r="B119" t="s">
+        <v>19</v>
+      </c>
+      <c r="C119" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119" s="3">
+        <f t="shared" si="2"/>
+        <v>26950</v>
+      </c>
+      <c r="E119" s="1">
+        <v>26950</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A120" t="s">
+        <v>25</v>
+      </c>
+      <c r="B120" t="s">
+        <v>19</v>
+      </c>
+      <c r="C120" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" s="3">
+        <f t="shared" si="2"/>
+        <v>32230</v>
+      </c>
+      <c r="E120" s="1">
+        <v>32230</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="B121" t="s">
+        <v>19</v>
+      </c>
+      <c r="C121" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" s="3">
+        <f t="shared" si="2"/>
+        <v>37290</v>
+      </c>
+      <c r="E121" s="1">
+        <v>37290</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A122" t="s">
+        <v>25</v>
+      </c>
+      <c r="B122" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" t="s">
+        <v>6</v>
+      </c>
+      <c r="D122" s="3">
+        <f t="shared" si="2"/>
+        <v>81840</v>
+      </c>
+      <c r="E122" s="1">
+        <v>81840</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A123" t="s">
+        <v>25</v>
+      </c>
+      <c r="B123" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" s="3">
+        <f t="shared" si="2"/>
+        <v>90530</v>
+      </c>
+      <c r="E123" s="1">
+        <v>90530</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A124" t="s">
+        <v>25</v>
+      </c>
+      <c r="B124" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="3">
+        <f t="shared" si="2"/>
+        <v>99220</v>
+      </c>
+      <c r="E124" s="1">
+        <v>99220</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A125" t="s">
+        <v>25</v>
+      </c>
+      <c r="B125" t="s">
+        <v>20</v>
+      </c>
+      <c r="C125" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="3">
+        <f t="shared" si="2"/>
+        <v>105600</v>
+      </c>
+      <c r="E125" s="1">
+        <v>105600</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A126" t="s">
+        <v>25</v>
+      </c>
+      <c r="B126" t="s">
+        <v>20</v>
+      </c>
+      <c r="C126" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="3">
+        <f t="shared" si="2"/>
+        <v>116600</v>
+      </c>
+      <c r="E126" s="1">
+        <v>116600</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B127" t="s">
+        <v>20</v>
+      </c>
+      <c r="C127" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="3">
+        <f t="shared" si="2"/>
+        <v>148940</v>
+      </c>
+      <c r="E127" s="1">
+        <v>148940</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A128" t="s">
+        <v>25</v>
+      </c>
+      <c r="B128" t="s">
+        <v>21</v>
+      </c>
+      <c r="C128" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" s="3">
+        <f t="shared" si="2"/>
+        <v>37290</v>
+      </c>
+      <c r="E128" s="1">
+        <v>37290</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A129" t="s">
+        <v>25</v>
+      </c>
+      <c r="B129" t="s">
+        <v>21</v>
+      </c>
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" s="3">
+        <f t="shared" si="2"/>
+        <v>41140</v>
+      </c>
+      <c r="E129" s="1">
+        <v>41140</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A130" t="s">
+        <v>25</v>
+      </c>
+      <c r="B130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C130" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" s="3">
+        <f t="shared" si="2"/>
+        <v>44990</v>
+      </c>
+      <c r="E130" s="1">
+        <v>44990</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="3">
+        <f t="shared" si="2"/>
+        <v>48070</v>
+      </c>
+      <c r="E131" s="1">
+        <v>48070</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A132" t="s">
+        <v>25</v>
+      </c>
+      <c r="B132" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" t="s">
+        <v>10</v>
+      </c>
+      <c r="D132" s="3">
+        <f t="shared" si="2"/>
+        <v>52910</v>
+      </c>
+      <c r="E132" s="1">
+        <v>52910</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A133" t="s">
+        <v>25</v>
+      </c>
+      <c r="B133" t="s">
+        <v>21</v>
+      </c>
+      <c r="C133" t="s">
+        <v>11</v>
+      </c>
+      <c r="D133" s="3">
+        <f t="shared" si="2"/>
+        <v>67760</v>
+      </c>
+      <c r="E133" s="1">
+        <v>67760</v>
       </c>
     </row>
   </sheetData>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss358115\Desktop\Keeperメニュー\Keeperメニュー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{472B4AAD-49E7-FF4A-8FA1-D4DE9DA54E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{73CF41AA-5CBE-5A4D-B378-BF1B5E7EF6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="27">
   <si>
     <t>商品名</t>
   </si>
@@ -122,10 +122,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>KeePer施工車限定</t>
+    <t>Keeper部分施工</t>
   </si>
   <si>
-    <t>Keeper部分施工</t>
+    <t>ミネラル取り洗車</t>
   </si>
 </sst>
 </file>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="3">
-        <f t="shared" ref="D3:D66" si="0">SUM(E3)*1</f>
+        <f t="shared" ref="D3:D72" si="0">SUM(E3)*1</f>
         <v>3510</v>
       </c>
       <c r="E3" s="1">
@@ -1133,955 +1133,955 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
       </c>
       <c r="C38" t="s">
         <v>6</v>
       </c>
       <c r="D38" s="3">
-        <f t="shared" si="0"/>
-        <v>124960</v>
-      </c>
-      <c r="E38" s="1">
-        <v>124960</v>
+        <v>540</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="3">
-        <f t="shared" si="0"/>
-        <v>136290</v>
-      </c>
-      <c r="E39" s="2">
-        <v>136290</v>
+        <v>540</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="3">
-        <f t="shared" si="0"/>
-        <v>148500</v>
-      </c>
-      <c r="E40" s="2">
-        <v>148500</v>
+        <v>540</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="3">
-        <f t="shared" si="0"/>
-        <v>165440</v>
-      </c>
-      <c r="E41" s="2">
-        <v>165440</v>
+        <v>540</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A42" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="3">
-        <f t="shared" si="0"/>
-        <v>176440</v>
-      </c>
-      <c r="E42" s="2">
-        <v>176440</v>
+        <v>540</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
       </c>
       <c r="C43" t="s">
         <v>11</v>
       </c>
       <c r="D43" s="3">
-        <f t="shared" si="0"/>
-        <v>192280</v>
-      </c>
-      <c r="E43" s="2">
-        <v>192280</v>
+        <v>540</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A44" t="s">
         <v>16</v>
       </c>
-      <c r="B44" t="s">
-        <v>15</v>
-      </c>
       <c r="C44" t="s">
         <v>6</v>
       </c>
       <c r="D44" s="3">
         <f t="shared" si="0"/>
-        <v>187440</v>
+        <v>124960</v>
       </c>
       <c r="E44" s="1">
-        <v>187440</v>
+        <v>124960</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A45" t="s">
         <v>16</v>
       </c>
-      <c r="B45" t="s">
-        <v>15</v>
-      </c>
       <c r="C45" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="3">
         <f t="shared" si="0"/>
-        <v>208780</v>
-      </c>
-      <c r="E45" s="1">
-        <v>208780</v>
+        <v>136290</v>
+      </c>
+      <c r="E45" s="2">
+        <v>136290</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A46" t="s">
         <v>16</v>
       </c>
-      <c r="B46" t="s">
-        <v>15</v>
-      </c>
       <c r="C46" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="3">
         <f t="shared" si="0"/>
-        <v>227590</v>
-      </c>
-      <c r="E46" s="1">
-        <v>227590</v>
+        <v>148500</v>
+      </c>
+      <c r="E46" s="2">
+        <v>148500</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A47" t="s">
         <v>16</v>
       </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
       <c r="C47" t="s">
         <v>9</v>
       </c>
       <c r="D47" s="3">
         <f t="shared" si="0"/>
-        <v>248050</v>
-      </c>
-      <c r="E47" s="1">
-        <v>248050</v>
+        <v>165440</v>
+      </c>
+      <c r="E47" s="2">
+        <v>165440</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A48" t="s">
         <v>16</v>
       </c>
-      <c r="B48" t="s">
-        <v>15</v>
-      </c>
       <c r="C48" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="3">
         <f t="shared" si="0"/>
-        <v>258830</v>
-      </c>
-      <c r="E48" s="1">
-        <v>258830</v>
+        <v>176440</v>
+      </c>
+      <c r="E48" s="2">
+        <v>176440</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A49" t="s">
         <v>16</v>
       </c>
-      <c r="B49" t="s">
-        <v>15</v>
-      </c>
       <c r="C49" t="s">
         <v>11</v>
       </c>
       <c r="D49" s="3">
         <f t="shared" si="0"/>
-        <v>294690</v>
-      </c>
-      <c r="E49" s="1">
-        <v>294690</v>
+        <v>192280</v>
+      </c>
+      <c r="E49" s="2">
+        <v>192280</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B50" t="s">
+        <v>15</v>
       </c>
       <c r="C50" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="3">
         <f t="shared" si="0"/>
-        <v>68310</v>
+        <v>187440</v>
       </c>
       <c r="E50" s="1">
-        <v>68310</v>
+        <v>187440</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="3">
         <f t="shared" si="0"/>
-        <v>74250</v>
-      </c>
-      <c r="E51" s="2">
-        <v>74250</v>
+        <v>208780</v>
+      </c>
+      <c r="E51" s="1">
+        <v>208780</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B52" t="s">
+        <v>15</v>
       </c>
       <c r="C52" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="3">
         <f t="shared" si="0"/>
-        <v>80300</v>
-      </c>
-      <c r="E52" s="2">
-        <v>80300</v>
+        <v>227590</v>
+      </c>
+      <c r="E52" s="1">
+        <v>227590</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
       </c>
       <c r="C53" t="s">
         <v>9</v>
       </c>
       <c r="D53" s="3">
         <f t="shared" si="0"/>
-        <v>84920</v>
-      </c>
-      <c r="E53" s="2">
-        <v>84920</v>
+        <v>248050</v>
+      </c>
+      <c r="E53" s="1">
+        <v>248050</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B54" t="s">
+        <v>15</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="3">
         <f t="shared" si="0"/>
-        <v>92180</v>
-      </c>
-      <c r="E54" s="2">
-        <v>92180</v>
+        <v>258830</v>
+      </c>
+      <c r="E54" s="1">
+        <v>258830</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="3">
         <f t="shared" si="0"/>
-        <v>114730</v>
-      </c>
-      <c r="E55" s="2">
-        <v>114730</v>
+        <v>294690</v>
+      </c>
+      <c r="E55" s="1">
+        <v>294690</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A56" t="s">
         <v>17</v>
       </c>
-      <c r="B56" t="s">
-        <v>15</v>
-      </c>
       <c r="C56" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="3">
         <f t="shared" si="0"/>
-        <v>109450</v>
+        <v>68310</v>
       </c>
       <c r="E56" s="1">
-        <v>109450</v>
+        <v>68310</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A57" t="s">
         <v>17</v>
       </c>
-      <c r="B57" t="s">
-        <v>15</v>
-      </c>
       <c r="C57" t="s">
         <v>7</v>
       </c>
       <c r="D57" s="3">
         <f t="shared" si="0"/>
-        <v>121500</v>
-      </c>
-      <c r="E57" s="1">
-        <v>121500</v>
+        <v>74250</v>
+      </c>
+      <c r="E57" s="2">
+        <v>74250</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A58" t="s">
         <v>17</v>
       </c>
-      <c r="B58" t="s">
-        <v>15</v>
-      </c>
       <c r="C58" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="3">
         <f t="shared" si="0"/>
-        <v>133760</v>
-      </c>
-      <c r="E58" s="1">
-        <v>133760</v>
+        <v>80300</v>
+      </c>
+      <c r="E58" s="2">
+        <v>80300</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A59" t="s">
         <v>17</v>
       </c>
-      <c r="B59" t="s">
-        <v>15</v>
-      </c>
       <c r="C59" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="3">
         <f t="shared" si="0"/>
-        <v>139920</v>
-      </c>
-      <c r="E59" s="1">
-        <v>139920</v>
+        <v>84920</v>
+      </c>
+      <c r="E59" s="2">
+        <v>84920</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A60" t="s">
         <v>17</v>
       </c>
-      <c r="B60" t="s">
-        <v>15</v>
-      </c>
       <c r="C60" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="3">
         <f t="shared" si="0"/>
-        <v>154330</v>
-      </c>
-      <c r="E60" s="1">
-        <v>154330</v>
+        <v>92180</v>
+      </c>
+      <c r="E60" s="2">
+        <v>92180</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A61" t="s">
         <v>17</v>
       </c>
-      <c r="B61" t="s">
-        <v>15</v>
-      </c>
       <c r="C61" t="s">
         <v>11</v>
       </c>
       <c r="D61" s="3">
         <f t="shared" si="0"/>
-        <v>192830</v>
-      </c>
-      <c r="E61" s="1">
-        <v>192830</v>
+        <v>114730</v>
+      </c>
+      <c r="E61" s="2">
+        <v>114730</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="B62" t="s">
+        <v>15</v>
       </c>
       <c r="C62" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="3">
         <f t="shared" si="0"/>
-        <v>31020</v>
+        <v>109450</v>
       </c>
       <c r="E62" s="1">
-        <v>31020</v>
+        <v>109450</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A63" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="B63" t="s">
+        <v>15</v>
       </c>
       <c r="C63" t="s">
         <v>7</v>
       </c>
       <c r="D63" s="3">
         <f t="shared" si="0"/>
-        <v>33330</v>
+        <v>121500</v>
       </c>
       <c r="E63" s="1">
-        <v>33330</v>
+        <v>121500</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="B64" t="s">
+        <v>15</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="3">
         <f t="shared" si="0"/>
-        <v>35970</v>
+        <v>133760</v>
       </c>
       <c r="E64" s="1">
-        <v>35970</v>
+        <v>133760</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="3">
         <f t="shared" si="0"/>
-        <v>38390</v>
+        <v>139920</v>
       </c>
       <c r="E65" s="1">
-        <v>38390</v>
+        <v>139920</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A66" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="B66" t="s">
+        <v>15</v>
       </c>
       <c r="C66" t="s">
         <v>10</v>
       </c>
       <c r="D66" s="3">
         <f t="shared" si="0"/>
-        <v>43560</v>
+        <v>154330</v>
       </c>
       <c r="E66" s="1">
-        <v>43560</v>
+        <v>154330</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A67" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="B67" t="s">
+        <v>15</v>
       </c>
       <c r="C67" t="s">
         <v>11</v>
       </c>
       <c r="D67" s="3">
-        <f t="shared" ref="D67:D91" si="1">SUM(E67)*1</f>
-        <v>48620</v>
+        <f t="shared" si="0"/>
+        <v>192830</v>
       </c>
       <c r="E67" s="1">
-        <v>48620</v>
+        <v>192830</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C68" t="s">
         <v>6</v>
       </c>
       <c r="D68" s="3">
+        <f t="shared" si="0"/>
+        <v>31020</v>
+      </c>
+      <c r="E68" s="1">
+        <v>31020</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="3">
+        <f t="shared" si="0"/>
+        <v>33330</v>
+      </c>
+      <c r="E69" s="1">
+        <v>33330</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="3">
+        <f t="shared" si="0"/>
+        <v>35970</v>
+      </c>
+      <c r="E70" s="1">
+        <v>35970</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="3">
+        <f t="shared" si="0"/>
+        <v>38390</v>
+      </c>
+      <c r="E71" s="1">
+        <v>38390</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="3">
+        <f t="shared" si="0"/>
+        <v>43560</v>
+      </c>
+      <c r="E72" s="1">
+        <v>43560</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="3">
+        <f t="shared" ref="D73:D97" si="1">SUM(E73)*1</f>
+        <v>48620</v>
+      </c>
+      <c r="E73" s="1">
+        <v>48620</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="3">
         <f t="shared" si="1"/>
         <v>19690</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E74" s="1">
         <v>19690</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A69" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A75" t="s">
         <v>19</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C75" t="s">
         <v>7</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D75" s="3">
         <f t="shared" si="1"/>
         <v>22000</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E75" s="1">
         <v>22000</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A70" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A76" t="s">
         <v>19</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C76" t="s">
         <v>8</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D76" s="3">
         <f t="shared" si="1"/>
         <v>24640</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E76" s="1">
         <v>24640</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A71" t="s">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A77" t="s">
         <v>19</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C77" t="s">
         <v>9</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D77" s="3">
         <f t="shared" si="1"/>
         <v>26950</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E77" s="1">
         <v>26950</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A72" t="s">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A78" t="s">
         <v>19</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C78" t="s">
         <v>10</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D78" s="3">
         <f t="shared" si="1"/>
         <v>32230</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E78" s="1">
         <v>32230</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A73" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.1">
+      <c r="A79" t="s">
         <v>19</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C79" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D79" s="3">
         <f t="shared" si="1"/>
         <v>37290</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E79" s="1">
         <v>37290</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A74" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74" t="s">
-        <v>6</v>
-      </c>
-      <c r="D74" s="3">
-        <f t="shared" si="1"/>
-        <v>81840</v>
-      </c>
-      <c r="E74" s="1">
-        <v>81840</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A75" t="s">
-        <v>20</v>
-      </c>
-      <c r="C75" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="3">
-        <f t="shared" si="1"/>
-        <v>90530</v>
-      </c>
-      <c r="E75" s="1">
-        <v>90530</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A76" t="s">
-        <v>20</v>
-      </c>
-      <c r="C76" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="3">
-        <f t="shared" si="1"/>
-        <v>99220</v>
-      </c>
-      <c r="E76" s="1">
-        <v>99220</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A77" t="s">
-        <v>20</v>
-      </c>
-      <c r="C77" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="3">
-        <f t="shared" si="1"/>
-        <v>105600</v>
-      </c>
-      <c r="E77" s="1">
-        <v>105600</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A78" t="s">
-        <v>20</v>
-      </c>
-      <c r="C78" t="s">
-        <v>10</v>
-      </c>
-      <c r="D78" s="3">
-        <f t="shared" si="1"/>
-        <v>116600</v>
-      </c>
-      <c r="E78" s="1">
-        <v>116600</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.1">
-      <c r="A79" t="s">
-        <v>20</v>
-      </c>
-      <c r="C79" t="s">
-        <v>11</v>
-      </c>
-      <c r="D79" s="3">
-        <f t="shared" si="1"/>
-        <v>148940</v>
-      </c>
-      <c r="E79" s="1">
-        <v>148940</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A80" t="s">
         <v>20</v>
       </c>
-      <c r="B80" t="s">
-        <v>15</v>
-      </c>
       <c r="C80" t="s">
         <v>6</v>
       </c>
       <c r="D80" s="3">
         <f t="shared" si="1"/>
-        <v>122870</v>
+        <v>81840</v>
       </c>
       <c r="E80" s="1">
-        <v>122870</v>
+        <v>81840</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A81" t="s">
         <v>20</v>
       </c>
-      <c r="B81" t="s">
-        <v>15</v>
-      </c>
       <c r="C81" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="3">
         <f t="shared" si="1"/>
-        <v>137720</v>
+        <v>90530</v>
       </c>
       <c r="E81" s="1">
-        <v>137720</v>
+        <v>90530</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A82" t="s">
         <v>20</v>
       </c>
-      <c r="B82" t="s">
-        <v>15</v>
-      </c>
       <c r="C82" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="3">
         <f t="shared" si="1"/>
-        <v>152680</v>
+        <v>99220</v>
       </c>
       <c r="E82" s="1">
-        <v>152680</v>
+        <v>99220</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A83" t="s">
         <v>20</v>
       </c>
-      <c r="B83" t="s">
-        <v>15</v>
-      </c>
       <c r="C83" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="3">
         <f t="shared" si="1"/>
-        <v>160050</v>
+        <v>105600</v>
       </c>
       <c r="E83" s="1">
-        <v>160050</v>
+        <v>105600</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A84" t="s">
         <v>20</v>
       </c>
-      <c r="B84" t="s">
-        <v>15</v>
-      </c>
       <c r="C84" t="s">
         <v>10</v>
       </c>
       <c r="D84" s="3">
         <f t="shared" si="1"/>
-        <v>178860</v>
+        <v>116600</v>
       </c>
       <c r="E84" s="1">
-        <v>178860</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A85" t="s">
         <v>20</v>
       </c>
-      <c r="B85" t="s">
-        <v>15</v>
-      </c>
       <c r="C85" t="s">
         <v>11</v>
       </c>
       <c r="D85" s="3">
         <f t="shared" si="1"/>
-        <v>227040</v>
+        <v>148940</v>
       </c>
       <c r="E85" s="1">
-        <v>227040</v>
+        <v>148940</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A86" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="B86" t="s">
+        <v>15</v>
       </c>
       <c r="C86" t="s">
         <v>6</v>
       </c>
       <c r="D86" s="3">
         <f t="shared" si="1"/>
-        <v>37290</v>
+        <v>122870</v>
       </c>
       <c r="E86" s="1">
-        <v>37290</v>
+        <v>122870</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A87" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="B87" t="s">
+        <v>15</v>
       </c>
       <c r="C87" t="s">
         <v>7</v>
       </c>
       <c r="D87" s="3">
         <f t="shared" si="1"/>
-        <v>41140</v>
+        <v>137720</v>
       </c>
       <c r="E87" s="1">
-        <v>41140</v>
+        <v>137720</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A88" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="B88" t="s">
+        <v>15</v>
       </c>
       <c r="C88" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="3">
         <f t="shared" si="1"/>
-        <v>44990</v>
+        <v>152680</v>
       </c>
       <c r="E88" s="1">
-        <v>44990</v>
+        <v>152680</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A89" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="B89" t="s">
+        <v>15</v>
       </c>
       <c r="C89" t="s">
         <v>9</v>
       </c>
       <c r="D89" s="3">
         <f t="shared" si="1"/>
-        <v>48070</v>
+        <v>160050</v>
       </c>
       <c r="E89" s="1">
-        <v>48070</v>
+        <v>160050</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A90" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="B90" t="s">
+        <v>15</v>
       </c>
       <c r="C90" t="s">
         <v>10</v>
       </c>
       <c r="D90" s="3">
         <f t="shared" si="1"/>
-        <v>52910</v>
+        <v>178860</v>
       </c>
       <c r="E90" s="1">
-        <v>52910</v>
+        <v>178860</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A91" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="B91" t="s">
+        <v>15</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
       </c>
       <c r="D91" s="3">
         <f t="shared" si="1"/>
-        <v>67760</v>
+        <v>227040</v>
       </c>
       <c r="E91" s="1">
-        <v>67760</v>
+        <v>227040</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A92" t="s">
-        <v>24</v>
-      </c>
-      <c r="B92" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C92" t="s">
         <v>6</v>
       </c>
       <c r="D92" s="3">
-        <v>540</v>
+        <f t="shared" si="1"/>
+        <v>37290</v>
+      </c>
+      <c r="E92" s="1">
+        <v>37290</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A93" t="s">
-        <v>24</v>
-      </c>
-      <c r="B93" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C93" t="s">
         <v>7</v>
       </c>
       <c r="D93" s="3">
-        <v>540</v>
+        <f t="shared" si="1"/>
+        <v>41140</v>
+      </c>
+      <c r="E93" s="1">
+        <v>41140</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A94" t="s">
-        <v>24</v>
-      </c>
-      <c r="B94" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C94" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="3">
-        <v>540</v>
+        <f t="shared" si="1"/>
+        <v>44990</v>
+      </c>
+      <c r="E94" s="1">
+        <v>44990</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A95" t="s">
-        <v>24</v>
-      </c>
-      <c r="B95" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C95" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="3">
-        <v>540</v>
+        <f t="shared" si="1"/>
+        <v>48070</v>
+      </c>
+      <c r="E95" s="1">
+        <v>48070</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A96" t="s">
-        <v>25</v>
-      </c>
-      <c r="B96" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C96" t="s">
         <v>10</v>
       </c>
       <c r="D96" s="3">
-        <v>540</v>
+        <f t="shared" si="1"/>
+        <v>52910</v>
+      </c>
+      <c r="E96" s="1">
+        <v>52910</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A97" t="s">
-        <v>25</v>
-      </c>
-      <c r="B97" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
         <v>11</v>
       </c>
       <c r="D97" s="3">
-        <v>540</v>
+        <f t="shared" si="1"/>
+        <v>67760</v>
+      </c>
+      <c r="E97" s="1">
+        <v>67760</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B98" t="s">
         <v>16</v>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B99" t="s">
         <v>16</v>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B100" t="s">
         <v>16</v>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B101" t="s">
         <v>16</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B102" t="s">
         <v>16</v>
@@ -2171,7 +2171,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B103" t="s">
         <v>16</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A104" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
@@ -2279,7 +2279,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B109" t="s">
         <v>17</v>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B110" t="s">
         <v>18</v>
@@ -2315,7 +2315,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B111" t="s">
         <v>18</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B112" t="s">
         <v>18</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B113" t="s">
         <v>18</v>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B114" t="s">
         <v>18</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A115" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B115" t="s">
         <v>18</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A116" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B116" t="s">
         <v>19</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B117" t="s">
         <v>19</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A118" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B118" t="s">
         <v>19</v>
@@ -2459,7 +2459,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A119" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B119" t="s">
         <v>19</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B120" t="s">
         <v>19</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B121" t="s">
         <v>19</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A122" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B122" t="s">
         <v>20</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A123" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B123" t="s">
         <v>20</v>
@@ -2549,7 +2549,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B124" t="s">
         <v>20</v>
@@ -2567,7 +2567,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B125" t="s">
         <v>20</v>
@@ -2585,7 +2585,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A126" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B126" t="s">
         <v>20</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B127" t="s">
         <v>20</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A128" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B128" t="s">
         <v>21</v>
@@ -2639,7 +2639,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A129" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B129" t="s">
         <v>21</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A130" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B130" t="s">
         <v>21</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A131" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B131" t="s">
         <v>21</v>
@@ -2693,7 +2693,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A132" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B132" t="s">
         <v>21</v>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.1">
       <c r="A133" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B133" t="s">
         <v>21</v>
